--- a/data/BASE_INTRA_ORCAMENTARIA_DETALHAMENTO.xlsx
+++ b/data/BASE_INTRA_ORCAMENTARIA_DETALHAMENTO.xlsx
@@ -499,7 +499,7 @@
         <v>617928493</v>
       </c>
       <c r="D5" t="n">
-        <v>1258967529</v>
+        <v>1258925701</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>7976441576</v>
       </c>
       <c r="D16" t="n">
-        <v>6558973245</v>
+        <v>6559015073</v>
       </c>
     </row>
     <row r="17">
